--- a/Lumbee_RIVR_Tech_IRU_Package/03_Operational_Schedules/Exhibit_C_Fiber_Allocation_and_Reserved_Capacity.xlsx
+++ b/Lumbee_RIVR_Tech_IRU_Package/03_Operational_Schedules/Exhibit_C_Fiber_Allocation_and_Reserved_Capacity.xlsx
@@ -604,6 +604,14 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Parties: Lumbee Tribe of North Carolina (the “Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -673,6 +681,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>

--- a/Lumbee_RIVR_Tech_IRU_Package/03_Operational_Schedules/Exhibit_C_Fiber_Allocation_and_Reserved_Capacity.xlsx
+++ b/Lumbee_RIVR_Tech_IRU_Package/03_Operational_Schedules/Exhibit_C_Fiber_Allocation_and_Reserved_Capacity.xlsx
@@ -607,7 +607,7 @@
     <row r="3">
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Parties: Lumbee Tribe of North Carolina (the “Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
+          <t>Parties: Lumbee Tribe of North Carolina (the “Lumbee Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>• Reserved Tribal strands are held for the Tribe's own governmental, educational, health, and public-safety use and are not marketed by RIVR Tech.</t>
+          <t>• Reserved Tribal strands are held for the Lumbee Tribe's own governmental, educational, health, and public-safety use and are not marketed by RIVR Tech.</t>
         </is>
       </c>
     </row>
